--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -109,12 +106,12 @@
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
+    <t>BELLO</t>
+  </si>
+  <si>
     <t>CUAQUEHUA</t>
   </si>
   <si>
@@ -133,10 +130,10 @@
     <t>EVANGELISTA</t>
   </si>
   <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
     <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>JOACIM ALBERTO</t>
   </si>
   <si>
     <t>MELANIE</t>
@@ -570,7 +567,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -796,16 +793,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90.91</v>
+      </c>
+      <c r="H5">
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -893,7 +893,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -962,16 +962,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>90.91</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1039,16 +1039,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920153</v>
+        <v>22330051920386</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1062,25 +1062,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920386</v>
+        <v>24330051920384</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1088,13 +1088,13 @@
         <v>22330051920158</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1111,13 +1111,13 @@
         <v>22330051920162</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1134,13 +1134,13 @@
         <v>22330051920299</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1157,13 +1157,13 @@
         <v>22330051920170</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1180,13 +1180,13 @@
         <v>22330051920172</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1203,13 +1203,13 @@
         <v>22330051920171</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1226,13 +1226,13 @@
         <v>22330051920282</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="53">
   <si>
     <t>Mat</t>
   </si>
@@ -82,39 +82,57 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
     <t>CORRO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
@@ -124,21 +142,27 @@
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
-    <t>GUSTAVO</t>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>NATHAN KARLO</t>
+  </si>
+  <si>
+    <t>CRUZ ARMANDO</t>
+  </si>
+  <si>
+    <t>RENATA</t>
+  </si>
+  <si>
+    <t>IRVIN</t>
   </si>
   <si>
     <t>JOACIM ALBERTO</t>
   </si>
   <si>
-    <t>MELANIE</t>
-  </si>
-  <si>
     <t>DINORAH AZUL</t>
   </si>
   <si>
@@ -149,9 +173,6 @@
   </si>
   <si>
     <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
   </si>
   <si>
     <t>SAUL KOURCHENKOV</t>
@@ -724,16 +745,19 @@
         <v>48</v>
       </c>
       <c r="D2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -747,16 +771,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -770,16 +797,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>83.78</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -819,16 +849,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>79.41</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -884,16 +917,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -910,16 +943,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>91.67</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -936,16 +969,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>83.78</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -988,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>67.65000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1007,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1039,22 +1072,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920386</v>
+        <v>24330051920132</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1062,45 +1095,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920384</v>
+        <v>24330051920216</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920158</v>
+        <v>24330051920097</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1108,22 +1141,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920162</v>
+        <v>24330051920095</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1131,22 +1164,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920299</v>
+        <v>24330051920318</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1154,22 +1187,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920170</v>
+        <v>24330051920384</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1177,16 +1210,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920172</v>
+        <v>22330051920162</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1200,16 +1233,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920171</v>
+        <v>22330051920299</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1223,16 +1256,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920282</v>
+        <v>22330051920170</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1241,6 +1274,52 @@
         <v>14</v>
       </c>
       <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920172</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920282</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="73">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,27 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>VILLARREAL</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -112,9 +133,27 @@
     <t>SUAREZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MACUISTLE</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>DE URIARTE</t>
+  </si>
+  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
@@ -143,6 +182,27 @@
   </si>
   <si>
     <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>SARA ALY</t>
+  </si>
+  <si>
+    <t>DIANA CAMILA</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>ESTRELLA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
+  </si>
+  <si>
+    <t>DAMARIZ</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
   </si>
   <si>
     <t>JESUS</t>
@@ -1040,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1072,62 +1132,62 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920132</v>
+        <v>24330051920040</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920216</v>
+        <v>24330051920038</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920097</v>
+        <v>24330051920129</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1136,21 +1196,21 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920095</v>
+        <v>24330051920250</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1159,142 +1219,142 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920318</v>
+        <v>24330051920347</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920384</v>
+        <v>23330051920341</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920162</v>
+        <v>24330051920060</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920299</v>
+        <v>24330051920132</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920170</v>
+        <v>24330051920216</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920172</v>
+        <v>24330051920097</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1302,24 +1362,185 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
+        <v>24330051920095</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920318</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920384</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920162</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920299</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920170</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920172</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
         <v>22330051920282</v>
       </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s">
         <v>9</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F19" t="s">
         <v>14</v>
       </c>
-      <c r="G12">
+      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="80">
   <si>
     <t>Mat</t>
   </si>
@@ -82,42 +82,51 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
     <t>MOTA</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
   </si>
   <si>
     <t>VILLARREAL</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -136,36 +145,39 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MACUISTLE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MACUISTLE</t>
+    <t>DE LA LUZ</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
+    <t>MACUIXTLE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>DE URIARTE</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>BELLO</t>
   </si>
   <si>
@@ -184,40 +196,49 @@
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>NAARA SAFIR</t>
+  </si>
+  <si>
+    <t>EDUARDO EMER</t>
+  </si>
+  <si>
+    <t>ESTRELLA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
+  </si>
+  <si>
     <t>SARA ALY</t>
   </si>
   <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>NATHAN KARLO</t>
+  </si>
+  <si>
+    <t>DAMARIZ</t>
+  </si>
+  <si>
     <t>DIANA CAMILA</t>
   </si>
   <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>ESTRELLA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
-  </si>
-  <si>
-    <t>DAMARIZ</t>
+    <t>CRUZ ARMANDO</t>
+  </si>
+  <si>
+    <t>RENATA</t>
+  </si>
+  <si>
+    <t>IRVIN</t>
   </si>
   <si>
     <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>NATHAN KARLO</t>
-  </si>
-  <si>
-    <t>CRUZ ARMANDO</t>
-  </si>
-  <si>
-    <t>RENATA</t>
-  </si>
-  <si>
-    <t>IRVIN</t>
   </si>
   <si>
     <t>JOACIM ALBERTO</t>
@@ -1100,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1132,22 +1153,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920040</v>
+        <v>24330051920348</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1155,22 +1176,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920038</v>
+        <v>24330051920162</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1178,25 +1199,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920129</v>
+        <v>22330051920150</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1207,10 +1228,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1230,10 +1251,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1247,16 +1268,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920341</v>
+        <v>24330051920040</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1270,25 +1291,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920060</v>
+        <v>24330051920129</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1299,10 +1320,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1322,10 +1343,10 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1339,30 +1360,30 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920097</v>
+        <v>23330051920341</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920095</v>
+        <v>24330051920038</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -1371,36 +1392,36 @@
         <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920318</v>
+        <v>24330051920097</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1408,22 +1429,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920384</v>
+        <v>24330051920095</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1431,22 +1452,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920162</v>
+        <v>24330051920318</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1454,22 +1475,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920299</v>
+        <v>24330051920060</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1477,22 +1498,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920170</v>
+        <v>24330051920384</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1500,16 +1521,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920172</v>
+        <v>22330051920162</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1523,16 +1544,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920282</v>
+        <v>22330051920299</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1541,6 +1562,75 @@
         <v>14</v>
       </c>
       <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920170</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920172</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920282</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="86">
   <si>
     <t>Mat</t>
   </si>
@@ -91,30 +91,36 @@
     <t>BAEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>CASTILLO</t>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>MOTA</t>
   </si>
   <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
     <t>PANZO</t>
   </si>
   <si>
@@ -151,24 +157,30 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
+  </si>
+  <si>
     <t>MARIN</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>MACUISTLE</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>MACUIXTLE</t>
   </si>
   <si>
@@ -205,28 +217,34 @@
     <t>EDUARDO EMER</t>
   </si>
   <si>
+    <t>CAROLINA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SARA ALY</t>
+  </si>
+  <si>
+    <t>NESTOR NOE</t>
+  </si>
+  <si>
     <t>ESTRELLA MONTSERRAT</t>
   </si>
   <si>
+    <t>JESUS</t>
+  </si>
+  <si>
     <t>ANGEL FRANCISCO</t>
   </si>
   <si>
-    <t>SARA ALY</t>
+    <t>NATHAN KARLO</t>
+  </si>
+  <si>
+    <t>DAMARIZ</t>
+  </si>
+  <si>
+    <t>DIANA CAMILA</t>
   </si>
   <si>
     <t>JUAN</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>NATHAN KARLO</t>
-  </si>
-  <si>
-    <t>DAMARIZ</t>
-  </si>
-  <si>
-    <t>DIANA CAMILA</t>
   </si>
   <si>
     <t>CRUZ ARMANDO</t>
@@ -1121,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1159,10 +1177,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1182,10 +1200,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1205,10 +1223,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1222,16 +1240,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920250</v>
+        <v>24330051920139</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1245,22 +1263,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920347</v>
+        <v>24330051920040</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1268,22 +1286,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920040</v>
+        <v>24330051920009</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1291,16 +1309,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920129</v>
+        <v>24330051920250</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1320,10 +1338,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1337,22 +1355,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920216</v>
+        <v>24330051920347</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1360,22 +1378,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920341</v>
+        <v>24330051920216</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1383,16 +1401,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920038</v>
+        <v>23330051920341</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1406,39 +1424,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920097</v>
+        <v>24330051920038</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920095</v>
+        <v>24330051920129</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1452,22 +1470,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920318</v>
+        <v>24330051920097</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1475,22 +1493,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920060</v>
+        <v>24330051920095</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1498,22 +1516,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920384</v>
+        <v>24330051920318</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1521,22 +1539,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920162</v>
+        <v>24330051920060</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1544,22 +1562,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920299</v>
+        <v>24330051920384</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1567,16 +1585,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920170</v>
+        <v>22330051920162</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1590,16 +1608,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920172</v>
+        <v>22330051920299</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1613,16 +1631,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920282</v>
+        <v>22330051920170</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1631,6 +1649,52 @@
         <v>14</v>
       </c>
       <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920172</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920282</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -85,196 +85,37 @@
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>BONILLA</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>VILLARREAL</t>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MACUISTLE</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MACUIXTLE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE URIARTE</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
     <t>VALERIA</t>
   </si>
   <si>
-    <t>NAARA SAFIR</t>
-  </si>
-  <si>
-    <t>EDUARDO EMER</t>
-  </si>
-  <si>
     <t>CAROLINA DEL CARMEN</t>
   </si>
   <si>
-    <t>SARA ALY</t>
-  </si>
-  <si>
     <t>NESTOR NOE</t>
   </si>
   <si>
-    <t>ESTRELLA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
-  </si>
-  <si>
-    <t>NATHAN KARLO</t>
-  </si>
-  <si>
-    <t>DAMARIZ</t>
-  </si>
-  <si>
-    <t>DIANA CAMILA</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>CRUZ ARMANDO</t>
-  </si>
-  <si>
-    <t>RENATA</t>
-  </si>
-  <si>
-    <t>IRVIN</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JOACIM ALBERTO</t>
-  </si>
-  <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
+    <t>DIEGO</t>
   </si>
 </sst>
 </file>
@@ -1016,16 +857,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1042,16 +883,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>91.67</v>
+        <v>97.22</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1068,16 +909,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>83.78</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1094,16 +935,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>90.91</v>
+        <v>93.94</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1120,13 +961,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>79.41</v>
+        <v>97.06</v>
       </c>
       <c r="H6">
         <v>7.1</v>
@@ -1139,7 +980,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1177,10 +1018,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1189,513 +1030,76 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920162</v>
+        <v>24330051920139</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920150</v>
+        <v>24330051920009</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920139</v>
+        <v>21330051920112</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920040</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920009</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920250</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
         <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920132</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920347</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920216</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920341</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920038</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920129</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920097</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920095</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920318</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920060</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920384</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920162</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920299</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920170</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920172</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920282</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
